--- a/fixtures/xlsx/row-heights/input.xlsx
+++ b/fixtures/xlsx/row-heights/input.xlsx
@@ -10,13 +10,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
+    <t>Header</t>
+  </si>
+  <si>
     <t>Tall row</t>
   </si>
   <si>
     <t>Normal row</t>
-  </si>
-  <si>
-    <t>Header</t>
   </si>
 </sst>
 </file>
@@ -26,17 +26,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/fixtures/xlsx/row-heights/input.xlsx
+++ b/fixtures/xlsx/row-heights/input.xlsx
@@ -13,10 +13,10 @@
     <t>Header</t>
   </si>
   <si>
-    <t>Tall row</t>
+    <t>Normal row</t>
   </si>
   <si>
-    <t>Normal row</t>
+    <t>Tall row</t>
   </si>
 </sst>
 </file>
@@ -31,12 +31,12 @@
     </row>
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
